--- a/data/trans_dic/P16A03-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A03-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,83; 8,86</t>
+          <t>3,81; 8,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,96</t>
+          <t>0,44; 3,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,76</t>
+          <t>0,43; 2,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,93</t>
+          <t>1,25; 3,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 7,68</t>
+          <t>2,95; 7,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,24; 9,78</t>
+          <t>4,03; 10,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 5,25</t>
+          <t>1,58; 5,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,42; 7,11</t>
+          <t>3,41; 6,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,85; 7,32</t>
+          <t>3,94; 7,43</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,08</t>
+          <t>2,21; 5,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,37</t>
+          <t>1,14; 3,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,67</t>
+          <t>2,65; 4,75</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,73</t>
+          <t>0,24; 2,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,94</t>
+          <t>0,46; 3,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,97</t>
+          <t>0,52; 2,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,75</t>
+          <t>0,62; 2,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 6,14</t>
+          <t>1,94; 6,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,9; 11,42</t>
+          <t>4,89; 11,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 7,66</t>
+          <t>2,7; 7,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 5,02</t>
+          <t>2,3; 5,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,85</t>
+          <t>1,39; 3,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,75; 6,16</t>
+          <t>2,82; 6,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,42</t>
+          <t>1,88; 4,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,32</t>
+          <t>1,51; 3,22</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,17</t>
+          <t>1,49; 4,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,4</t>
+          <t>0,82; 3,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,21</t>
+          <t>0,31; 2,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,4</t>
+          <t>0,45; 3,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 12,86</t>
+          <t>4,42; 12,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 7,66</t>
+          <t>2,12; 7,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 10,34</t>
+          <t>2,67; 10,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,4; 13,95</t>
+          <t>6,22; 13,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,36</t>
+          <t>2,53; 5,31</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,02</t>
+          <t>1,51; 3,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,51</t>
+          <t>1,15; 3,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,27</t>
+          <t>1,36; 5,22</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,32</t>
+          <t>0,95; 2,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,84</t>
+          <t>0,59; 1,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,58</t>
+          <t>1,03; 2,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,29</t>
+          <t>1,6; 3,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,14</t>
+          <t>3,13; 6,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,35; 8,03</t>
+          <t>4,44; 7,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,61; 5,63</t>
+          <t>2,72; 5,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,08</t>
+          <t>1,82; 5,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,48</t>
+          <t>1,95; 3,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,86</t>
+          <t>2,29; 3,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,4</t>
+          <t>1,93; 3,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 3,75</t>
+          <t>2,1; 3,74</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,65</t>
+          <t>1,05; 4,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,7</t>
+          <t>0,57; 2,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,28</t>
+          <t>0,55; 2,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,3</t>
+          <t>1,58; 4,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,38</t>
+          <t>2,22; 5,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,2; 8,88</t>
+          <t>5,3; 9,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,71</t>
+          <t>2,74; 5,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,91; 6,81</t>
+          <t>3,93; 6,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,42</t>
+          <t>2,11; 4,58</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,47; 5,97</t>
+          <t>3,6; 6,18</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,75</t>
+          <t>1,96; 3,58</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 5,39</t>
+          <t>3,44; 5,46</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1427,52 +1427,52 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,96</t>
+          <t>0,0; 3,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,54; 8,44</t>
+          <t>5,58; 8,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,6</t>
+          <t>3,88; 6,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,24; 5,86</t>
+          <t>3,2; 5,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,32; 7,3</t>
+          <t>4,27; 7,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,59; 6,85</t>
+          <t>4,5; 6,93</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,25; 5,52</t>
+          <t>3,29; 5,62</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,51; 4,5</t>
+          <t>2,59; 4,69</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,23; 5,7</t>
+          <t>3,34; 5,69</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,84</t>
+          <t>1,77; 2,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,8</t>
+          <t>0,94; 1,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,7</t>
+          <t>0,93; 1,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,57</t>
+          <t>1,55; 2,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,59; 6,12</t>
+          <t>4,63; 6,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,25; 6,88</t>
+          <t>5,17; 6,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,52; 4,95</t>
+          <t>3,53; 4,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,98; 5,59</t>
+          <t>4,04; 5,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,34; 4,3</t>
+          <t>3,33; 4,27</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,27; 4,2</t>
+          <t>3,24; 4,19</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,36; 3,17</t>
+          <t>2,36; 3,16</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,97; 3,93</t>
+          <t>2,88; 3,97</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18143; 41968</t>
+          <t>18039; 40598</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1890; 12928</t>
+          <t>1915; 13991</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1955; 11853</t>
+          <t>1851; 11796</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6476; 19854</t>
+          <t>6312; 19765</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9053; 23552</t>
+          <t>9051; 24155</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13340; 30739</t>
+          <t>12677; 31907</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5341; 18227</t>
+          <t>5493; 20002</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15293; 31809</t>
+          <t>15254; 31225</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30041; 57155</t>
+          <t>30734; 58018</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16946; 38205</t>
+          <t>16606; 37936</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9241; 26134</t>
+          <t>8817; 27158</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24412; 44496</t>
+          <t>25239; 45275</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>882; 10013</t>
+          <t>897; 10728</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1918; 16431</t>
+          <t>1899; 16196</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1990; 11216</t>
+          <t>1964; 11146</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2436; 12453</t>
+          <t>2813; 12284</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7951; 22837</t>
+          <t>7200; 22600</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16382; 38186</t>
+          <t>16343; 39085</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10484; 28524</t>
+          <t>10068; 27852</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8206; 19216</t>
+          <t>8791; 19116</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9961; 28445</t>
+          <t>10298; 28827</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20690; 46269</t>
+          <t>21215; 47528</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14346; 33160</t>
+          <t>14065; 33316</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13754; 27674</t>
+          <t>12596; 26848</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7913; 22606</t>
+          <t>8090; 22356</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4987; 21292</t>
+          <t>5161; 22661</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1808; 11538</t>
+          <t>1594; 10714</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2936; 22754</t>
+          <t>3006; 24558</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7368; 21577</t>
+          <t>7411; 21485</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5456; 19747</t>
+          <t>5476; 18415</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4543; 17179</t>
+          <t>4443; 17137</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10683; 23277</t>
+          <t>10385; 22365</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18118; 38032</t>
+          <t>17965; 37713</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13805; 35569</t>
+          <t>13389; 33641</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8213; 24145</t>
+          <t>7881; 23677</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11022; 44014</t>
+          <t>11383; 43566</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11961; 28779</t>
+          <t>11764; 31015</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7069; 21332</t>
+          <t>6795; 20577</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11567; 29638</t>
+          <t>11798; 29709</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17424; 34063</t>
+          <t>16553; 33292</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22288; 43862</t>
+          <t>22369; 46849</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33294; 61480</t>
+          <t>34002; 61165</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21577; 46515</t>
+          <t>22438; 45950</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16473; 49681</t>
+          <t>17787; 49478</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38689; 68040</t>
+          <t>38045; 66023</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>43419; 74253</t>
+          <t>44089; 74133</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38525; 67123</t>
+          <t>38030; 67894</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>40486; 75514</t>
+          <t>42192; 75301</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3592; 16247</t>
+          <t>3674; 16174</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2959; 13777</t>
+          <t>2925; 12998</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3505; 14176</t>
+          <t>3436; 14733</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7796; 20380</t>
+          <t>7477; 21203</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12447; 30613</t>
+          <t>12600; 31672</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>39428; 67356</t>
+          <t>40164; 70155</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19552; 42133</t>
+          <t>20236; 41875</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>32812; 57131</t>
+          <t>33012; 56648</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19701; 40557</t>
+          <t>19339; 42071</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44084; 75784</t>
+          <t>45678; 78405</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26565; 50931</t>
+          <t>26639; 48698</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>46333; 70801</t>
+          <t>45151; 71685</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4717</t>
+          <t>0; 5227</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>934; 7765</t>
+          <t>935; 7749</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5275</t>
+          <t>0; 4722</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 14342</t>
+          <t>0; 9470</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>69238; 105363</t>
+          <t>69630; 104368</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>41153; 72969</t>
+          <t>42859; 72457</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35025; 63394</t>
+          <t>34673; 63593</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>32804; 55523</t>
+          <t>32446; 55652</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>71056; 105947</t>
+          <t>69640; 107222</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>44614; 75740</t>
+          <t>45138; 77089</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34361; 61661</t>
+          <t>35477; 64179</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>32277; 57047</t>
+          <t>33428; 56905</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>55918; 92869</t>
+          <t>57993; 92911</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>32686; 61314</t>
+          <t>32068; 61790</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>31316; 57526</t>
+          <t>31412; 58028</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>51697; 86880</t>
+          <t>52228; 87457</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>154944; 206636</t>
+          <t>156300; 208895</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>185728; 243409</t>
+          <t>182855; 242351</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>124329; 174909</t>
+          <t>124614; 171778</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>142100; 199609</t>
+          <t>144250; 199676</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>222161; 286139</t>
+          <t>221420; 283864</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>227436; 291868</t>
+          <t>224885; 291210</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>163107; 219410</t>
+          <t>163305; 218273</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>206178; 273133</t>
+          <t>200029; 275492</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A03-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A03-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,81; 8,57</t>
+          <t>3,8; 8,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,2</t>
+          <t>0,43; 2,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,75</t>
+          <t>0,49; 2,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,91</t>
+          <t>1,14; 3,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 7,88</t>
+          <t>2,79; 7,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,03; 10,15</t>
+          <t>3,84; 9,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,76</t>
+          <t>1,53; 5,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,98</t>
+          <t>3,24; 6,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,94; 7,43</t>
+          <t>3,86; 7,33</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,05</t>
+          <t>2,27; 5,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,5</t>
+          <t>1,19; 3,41</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 4,75</t>
+          <t>2,56; 4,61</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,92</t>
+          <t>0,24; 2,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,88</t>
+          <t>0,47; 3,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,95</t>
+          <t>0,53; 3,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,72</t>
+          <t>0,58; 2,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,94; 6,08</t>
+          <t>2,08; 6,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 11,69</t>
+          <t>4,95; 11,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 7,48</t>
+          <t>2,72; 7,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,3; 5,0</t>
+          <t>2,17; 4,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,9</t>
+          <t>1,36; 3,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 6,33</t>
+          <t>2,87; 6,21</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,45</t>
+          <t>1,99; 4,64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,22</t>
+          <t>1,62; 3,28</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,12</t>
+          <t>1,48; 4,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,62</t>
+          <t>0,84; 3,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,05</t>
+          <t>0,36; 2,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,67</t>
+          <t>1,61; 4,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,42; 12,81</t>
+          <t>4,29; 12,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 7,14</t>
+          <t>2,05; 7,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 10,32</t>
+          <t>2,55; 10,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,22; 13,4</t>
+          <t>6,72; 14,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,31</t>
+          <t>2,59; 5,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,8</t>
+          <t>1,47; 3,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,44</t>
+          <t>1,24; 3,45</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,22</t>
+          <t>3,44; 6,6</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,5</t>
+          <t>0,93; 2,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,78</t>
+          <t>0,55; 1,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,58</t>
+          <t>1,01; 2,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,22</t>
+          <t>1,77; 3,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 6,56</t>
+          <t>3,07; 6,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,44; 7,99</t>
+          <t>4,44; 8,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,56</t>
+          <t>2,83; 5,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,06</t>
+          <t>3,89; 6,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,38</t>
+          <t>1,97; 3,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 3,86</t>
+          <t>2,27; 3,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 3,44</t>
+          <t>1,95; 3,45</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,74</t>
+          <t>2,97; 4,44</t>
         </is>
       </c>
     </row>
@@ -1224,47 +1224,47 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6,89%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4,01%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3,11%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
           <t>2,74%</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,89%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,01%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>5,4%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,63</t>
+          <t>1,02; 4,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,55</t>
+          <t>0,58; 2,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,37</t>
+          <t>0,56; 2,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,48</t>
+          <t>1,53; 4,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,22; 5,57</t>
+          <t>2,31; 5,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,3; 9,25</t>
+          <t>5,17; 9,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,74; 5,67</t>
+          <t>2,67; 5,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,93; 6,75</t>
+          <t>4,95; 7,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,58</t>
+          <t>2,11; 4,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,6; 6,18</t>
+          <t>3,61; 5,93</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,58</t>
+          <t>2,01; 3,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,44; 5,46</t>
+          <t>3,83; 5,64</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,92</t>
+          <t>0,35; 2,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,94</t>
+          <t>0,0; 3,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,58; 8,36</t>
+          <t>5,56; 8,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,88; 6,56</t>
+          <t>3,83; 6,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,2; 5,88</t>
+          <t>3,14; 5,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,27; 7,32</t>
+          <t>4,01; 6,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,5; 6,93</t>
+          <t>4,54; 6,88</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,29; 5,62</t>
+          <t>3,31; 5,63</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,59; 4,69</t>
+          <t>2,53; 4,6</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,69</t>
+          <t>3,18; 5,39</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1557,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,77; 2,84</t>
+          <t>1,72; 2,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 1,81</t>
+          <t>0,93; 1,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,71</t>
+          <t>0,91; 1,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,59</t>
+          <t>1,81; 2,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,63; 6,18</t>
+          <t>4,56; 6,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,17; 6,85</t>
+          <t>5,19; 6,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,53; 4,86</t>
+          <t>3,52; 4,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,04; 5,59</t>
+          <t>4,64; 5,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,33; 4,27</t>
+          <t>3,36; 4,29</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1607,12 +1607,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,36; 3,16</t>
+          <t>2,37; 3,15</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,88; 3,97</t>
+          <t>3,44; 4,24</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11711</t>
+          <t>11901</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21859</t>
+          <t>23555</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33570</t>
+          <t>35457</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18039; 40598</t>
+          <t>17986; 41098</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1915; 13991</t>
+          <t>1868; 13046</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1851; 11796</t>
+          <t>2101; 11773</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6312; 19765</t>
+          <t>6271; 19866</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9051; 24155</t>
+          <t>8549; 22938</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12677; 31907</t>
+          <t>12078; 31042</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5493; 20002</t>
+          <t>5293; 18808</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15254; 31225</t>
+          <t>15846; 32870</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30734; 58018</t>
+          <t>30108; 57224</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16606; 37936</t>
+          <t>17042; 37549</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8817; 27158</t>
+          <t>9263; 26453</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25239; 45275</t>
+          <t>26571; 47861</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6150</t>
+          <t>6839</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13020</t>
+          <t>13870</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19170</t>
+          <t>20709</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>897; 10728</t>
+          <t>883; 10119</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1899; 16196</t>
+          <t>1952; 15669</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1964; 11146</t>
+          <t>1997; 12092</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2813; 12284</t>
+          <t>2788; 13129</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7200; 22600</t>
+          <t>7728; 22295</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16343; 39085</t>
+          <t>16537; 37446</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10068; 27852</t>
+          <t>10131; 27306</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8791; 19116</t>
+          <t>9190; 20416</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10298; 28827</t>
+          <t>10070; 27836</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21215; 47528</t>
+          <t>21561; 46624</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14065; 33316</t>
+          <t>14893; 34769</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12596; 26848</t>
+          <t>14728; 29693</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12107</t>
+          <t>13240</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15980</t>
+          <t>18060</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28087</t>
+          <t>31300</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8090; 22356</t>
+          <t>8029; 22254</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5161; 22661</t>
+          <t>5241; 22982</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1594; 10714</t>
+          <t>1892; 10849</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3006; 24558</t>
+          <t>7586; 22566</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7411; 21485</t>
+          <t>7193; 21597</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5476; 18415</t>
+          <t>5289; 18750</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4443; 17137</t>
+          <t>4229; 17405</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10385; 22365</t>
+          <t>12593; 26716</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17965; 37713</t>
+          <t>18426; 38178</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13389; 33641</t>
+          <t>12981; 34673</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7881; 23677</t>
+          <t>8555; 23749</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11383; 43566</t>
+          <t>22671; 43483</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24136</t>
+          <t>29259</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>36230</t>
+          <t>42077</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>60366</t>
+          <t>71336</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11764; 31015</t>
+          <t>11523; 30088</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6795; 20577</t>
+          <t>6340; 21002</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11798; 29709</t>
+          <t>11603; 30021</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16553; 33292</t>
+          <t>20033; 42670</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22369; 46849</t>
+          <t>21945; 43418</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34002; 61165</t>
+          <t>33970; 62237</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22438; 45950</t>
+          <t>23336; 46297</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17787; 49478</t>
+          <t>33455; 53449</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38045; 66023</t>
+          <t>38389; 66344</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44089; 74133</t>
+          <t>43698; 74657</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38030; 67894</t>
+          <t>38434; 68228</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>42192; 75301</t>
+          <t>59181; 88546</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12966</t>
+          <t>14146</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>45321</t>
+          <t>50645</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>58287</t>
+          <t>64791</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3674; 16174</t>
+          <t>3569; 15970</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2925; 12998</t>
+          <t>2961; 13585</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3436; 14733</t>
+          <t>3465; 14057</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7477; 21203</t>
+          <t>8676; 23319</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12600; 31672</t>
+          <t>13116; 32223</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>40164; 70155</t>
+          <t>39206; 68340</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20236; 41875</t>
+          <t>19689; 42130</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>33012; 56648</t>
+          <t>41120; 61787</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19339; 42071</t>
+          <t>19418; 40647</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>45678; 78405</t>
+          <t>45860; 75200</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26639; 48698</t>
+          <t>27354; 52241</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>45151; 71685</t>
+          <t>53471; 78749</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>42107</t>
+          <t>42427</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>43913</t>
+          <t>44082</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5227</t>
+          <t>0; 4289</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>935; 7749</t>
+          <t>938; 7868</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4722</t>
+          <t>0; 5387</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 9470</t>
+          <t>0; 7235</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>69630; 104368</t>
+          <t>69486; 105935</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42859; 72457</t>
+          <t>42289; 73010</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34673; 63593</t>
+          <t>33967; 63671</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>32446; 55652</t>
+          <t>33806; 55804</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>69640; 107222</t>
+          <t>70247; 106417</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>45138; 77089</t>
+          <t>45448; 77214</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>35477; 64179</t>
+          <t>34659; 62971</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>33428; 56905</t>
+          <t>34322; 58216</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>68876</t>
+          <t>77041</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>174516</t>
+          <t>190635</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>243392</t>
+          <t>267675</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>57993; 92911</t>
+          <t>56361; 92952</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>32068; 61790</t>
+          <t>31747; 62021</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>31412; 58028</t>
+          <t>30843; 58498</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>52228; 87457</t>
+          <t>62111; 97143</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>156300; 208895</t>
+          <t>154198; 205219</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>182855; 242351</t>
+          <t>183529; 243064</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>124614; 171778</t>
+          <t>124277; 170960</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>144250; 199676</t>
+          <t>168653; 213909</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>221420; 283864</t>
+          <t>223608; 285025</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>224885; 291210</t>
+          <t>225276; 291395</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>163305; 218273</t>
+          <t>163681; 217564</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>200029; 275492</t>
+          <t>243438; 299827</t>
         </is>
       </c>
     </row>
